--- a/report-2026-06-06.xlsx
+++ b/report-2026-06-06.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="1098">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="1152">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-06T00:05:00+05:30</t>
+    <t>Generated 2026-06-06T02:14:57+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-06T00:03:04+05:30 (1m55s ago)</t>
+    <t>2026-06-06T02:12:57+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>4</t>
+    <t>1</t>
   </si>
   <si>
     <t>Last error</t>
@@ -3304,10 +3304,172 @@
     <t>00:03:04.533</t>
   </si>
   <si>
+    <t>2026-06-06T00:08:04.3890711+05:30</t>
+  </si>
+  <si>
+    <t>00:08:04.389</t>
+  </si>
+  <si>
+    <t>2026-06-06T00:13:04.2945198+05:30</t>
+  </si>
+  <si>
+    <t>00:13:04.294</t>
+  </si>
+  <si>
+    <t>2026-06-06T00:18:04.349719+05:30</t>
+  </si>
+  <si>
+    <t>00:18:04.349</t>
+  </si>
+  <si>
+    <t>2026-06-06T00:23:03.2036477+05:30</t>
+  </si>
+  <si>
+    <t>00:23:03.203</t>
+  </si>
+  <si>
+    <t>2026-06-06T00:23:03.20476+05:30</t>
+  </si>
+  <si>
+    <t>00:23:03.204</t>
+  </si>
+  <si>
+    <t>2026-06-06T00:28:04.4524866+05:30</t>
+  </si>
+  <si>
+    <t>00:28:04.452</t>
+  </si>
+  <si>
+    <t>2026-06-06T00:33:04.9882474+05:30</t>
+  </si>
+  <si>
+    <t>00:33:04.988</t>
+  </si>
+  <si>
+    <t>2026-06-06T00:38:04.4578185+05:30</t>
+  </si>
+  <si>
+    <t>00:38:04.457</t>
+  </si>
+  <si>
+    <t>2026-06-06T00:43:04.4165849+05:30</t>
+  </si>
+  <si>
+    <t>00:43:04.416</t>
+  </si>
+  <si>
+    <t>2026-06-06T00:48:04.4972065+05:30</t>
+  </si>
+  <si>
+    <t>00:48:04.497</t>
+  </si>
+  <si>
+    <t>2026-06-06T00:53:04.4158628+05:30</t>
+  </si>
+  <si>
+    <t>00:53:04.415</t>
+  </si>
+  <si>
+    <t>2026-06-06T00:58:04.746462+05:30</t>
+  </si>
+  <si>
+    <t>00:58:04.746</t>
+  </si>
+  <si>
+    <t>2026-06-06T01:03:04.2965606+05:30</t>
+  </si>
+  <si>
+    <t>01:03:04.296</t>
+  </si>
+  <si>
+    <t>2026-06-06T01:08:04.4870498+05:30</t>
+  </si>
+  <si>
+    <t>01:08:04.487</t>
+  </si>
+  <si>
+    <t>2026-06-06T01:13:04.3971229+05:30</t>
+  </si>
+  <si>
+    <t>01:13:04.397</t>
+  </si>
+  <si>
+    <t>2026-06-06T01:18:04.3982097+05:30</t>
+  </si>
+  <si>
+    <t>01:18:04.398</t>
+  </si>
+  <si>
+    <t>2026-06-06T01:23:04.338193+05:30</t>
+  </si>
+  <si>
+    <t>01:23:04.338</t>
+  </si>
+  <si>
+    <t>2026-06-06T01:28:04.3749159+05:30</t>
+  </si>
+  <si>
+    <t>01:28:04.374</t>
+  </si>
+  <si>
+    <t>2026-06-06T01:33:04.3612467+05:30</t>
+  </si>
+  <si>
+    <t>01:33:04.361</t>
+  </si>
+  <si>
+    <t>2026-06-06T01:38:04.5068535+05:30</t>
+  </si>
+  <si>
+    <t>01:38:04.506</t>
+  </si>
+  <si>
+    <t>2026-06-06T01:43:04.4507225+05:30</t>
+  </si>
+  <si>
+    <t>01:43:04.450</t>
+  </si>
+  <si>
+    <t>2026-06-06T01:48:04.4562151+05:30</t>
+  </si>
+  <si>
+    <t>01:48:04.456</t>
+  </si>
+  <si>
+    <t>2026-06-06T01:53:04.4814572+05:30</t>
+  </si>
+  <si>
+    <t>01:53:04.481</t>
+  </si>
+  <si>
+    <t>2026-06-06T01:58:04.3490827+05:30</t>
+  </si>
+  <si>
+    <t>01:58:04.349</t>
+  </si>
+  <si>
+    <t>2026-06-06T02:03:04.395145+05:30</t>
+  </si>
+  <si>
+    <t>02:03:04.395</t>
+  </si>
+  <si>
+    <t>2026-06-06T02:08:04.4247916+05:30</t>
+  </si>
+  <si>
+    <t>02:08:04.424</t>
+  </si>
+  <si>
+    <t>2026-06-06T02:12:57.4419603+05:30</t>
+  </si>
+  <si>
+    <t>02:12:57.441</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-06T00:05:00+05:30</t>
+    <t>2026-06-06T02:14:57+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -3862,7 +4024,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.58</t>
+          <t>10.0.59</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -3902,12 +4064,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 17m 11s</t>
+          <t>0h 2m 15s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-05 23:47:48</t>
+          <t>2026-06-06 02:12:42</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -3917,12 +4079,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-05 23:47:48</t>
+          <t>2026-06-06 02:12:42</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1h 14m 49s</t>
+          <t>2h 50m 9s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -3932,7 +4094,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>00:05:00</t>
+          <t>02:14:57</t>
         </is>
       </c>
     </row>
@@ -3969,7 +4131,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.58</t>
+          <t>10.0.59</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -3989,17 +4151,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>232.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>239231.5</t>
+          <t>113683.3</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>6873</t>
+          <t>954</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -4024,12 +4186,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-05 23:47:48</t>
+          <t>2026-06-06 02:12:42</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0h 57m 49s</t>
+          <t>2h 49m 44s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -4039,7 +4201,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>00:05:00</t>
+          <t>02:14:57</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4320,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-06T00:03:04.5336367+05:30</t>
+          <t>2026-06-06T02:12:57.4419603+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4168,7 +4330,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00:03:04.533</t>
+          <t>02:12:57.441</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -33875,18 +34037,1044 @@
         <v>43</v>
       </c>
     </row>
+    <row r="540">
+      <c r="A540" s="4">
+        <v>523</v>
+      </c>
+      <c r="B540" s="4" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C540" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D540" s="4" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E540" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F540" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G540" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H540" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I540" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J540" s="4">
+        <v>0</v>
+      </c>
+      <c r="K540" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L540" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="541">
-      <c r="A541" t="s">
-        <v>1095</v>
-      </c>
-      <c r="B541" t="s">
-        <v>1096</v>
-      </c>
-      <c r="D541" t="s">
+      <c r="A541" s="4">
+        <v>524</v>
+      </c>
+      <c r="B541" s="4" t="s">
         <v>1097</v>
       </c>
-      <c r="E541">
-        <v>522</v>
+      <c r="C541" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D541" s="4" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E541" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F541" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G541" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H541" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I541" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J541" s="4">
+        <v>0</v>
+      </c>
+      <c r="K541" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L541" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="4">
+        <v>525</v>
+      </c>
+      <c r="B542" s="4" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C542" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D542" s="4" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E542" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F542" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G542" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H542" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I542" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J542" s="4">
+        <v>0</v>
+      </c>
+      <c r="K542" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L542" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="3">
+        <v>526</v>
+      </c>
+      <c r="B543" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C543" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D543" s="3" t="s">
+        <v>1102</v>
+      </c>
+      <c r="E543" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F543" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G543" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H543" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I543" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J543" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K543" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L543" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="3">
+        <v>527</v>
+      </c>
+      <c r="B544" s="3" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C544" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D544" s="3" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E544" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F544" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G544" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H544" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I544" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J544" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K544" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L544" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="4">
+        <v>528</v>
+      </c>
+      <c r="B545" s="4" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C545" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D545" s="4" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E545" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F545" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G545" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H545" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I545" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J545" s="4">
+        <v>0</v>
+      </c>
+      <c r="K545" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L545" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="4">
+        <v>529</v>
+      </c>
+      <c r="B546" s="4" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C546" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D546" s="4" t="s">
+        <v>1108</v>
+      </c>
+      <c r="E546" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F546" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G546" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H546" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I546" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J546" s="4">
+        <v>0</v>
+      </c>
+      <c r="K546" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L546" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="4">
+        <v>530</v>
+      </c>
+      <c r="B547" s="4" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C547" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D547" s="4" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E547" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F547" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G547" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H547" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I547" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J547" s="4">
+        <v>0</v>
+      </c>
+      <c r="K547" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L547" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="4">
+        <v>531</v>
+      </c>
+      <c r="B548" s="4" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C548" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D548" s="4" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E548" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F548" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G548" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H548" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I548" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J548" s="4">
+        <v>0</v>
+      </c>
+      <c r="K548" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L548" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="4">
+        <v>532</v>
+      </c>
+      <c r="B549" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C549" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D549" s="4" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E549" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F549" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G549" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H549" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I549" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J549" s="4">
+        <v>0</v>
+      </c>
+      <c r="K549" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L549" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="4">
+        <v>533</v>
+      </c>
+      <c r="B550" s="4" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C550" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D550" s="4" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E550" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F550" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G550" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H550" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I550" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J550" s="4">
+        <v>0</v>
+      </c>
+      <c r="K550" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L550" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="4">
+        <v>534</v>
+      </c>
+      <c r="B551" s="4" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C551" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D551" s="4" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E551" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F551" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G551" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H551" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I551" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J551" s="4">
+        <v>0</v>
+      </c>
+      <c r="K551" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L551" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="4">
+        <v>535</v>
+      </c>
+      <c r="B552" s="4" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C552" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D552" s="4" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E552" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F552" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G552" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H552" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I552" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J552" s="4">
+        <v>0</v>
+      </c>
+      <c r="K552" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L552" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="4">
+        <v>536</v>
+      </c>
+      <c r="B553" s="4" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C553" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D553" s="4" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E553" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F553" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G553" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H553" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I553" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J553" s="4">
+        <v>0</v>
+      </c>
+      <c r="K553" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L553" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="4">
+        <v>537</v>
+      </c>
+      <c r="B554" s="4" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C554" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D554" s="4" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E554" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F554" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G554" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H554" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I554" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J554" s="4">
+        <v>0</v>
+      </c>
+      <c r="K554" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L554" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="4">
+        <v>538</v>
+      </c>
+      <c r="B555" s="4" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C555" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D555" s="4" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E555" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F555" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G555" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H555" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I555" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J555" s="4">
+        <v>0</v>
+      </c>
+      <c r="K555" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L555" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="4">
+        <v>539</v>
+      </c>
+      <c r="B556" s="4" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C556" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D556" s="4" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E556" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F556" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G556" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H556" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I556" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J556" s="4">
+        <v>0</v>
+      </c>
+      <c r="K556" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L556" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="4">
+        <v>540</v>
+      </c>
+      <c r="B557" s="4" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C557" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D557" s="4" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E557" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F557" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G557" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H557" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I557" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J557" s="4">
+        <v>0</v>
+      </c>
+      <c r="K557" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L557" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="4">
+        <v>541</v>
+      </c>
+      <c r="B558" s="4" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C558" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D558" s="4" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E558" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F558" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G558" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H558" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I558" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J558" s="4">
+        <v>0</v>
+      </c>
+      <c r="K558" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L558" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="4">
+        <v>542</v>
+      </c>
+      <c r="B559" s="4" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C559" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D559" s="4" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E559" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F559" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G559" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H559" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I559" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J559" s="4">
+        <v>0</v>
+      </c>
+      <c r="K559" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L559" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="4">
+        <v>543</v>
+      </c>
+      <c r="B560" s="4" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C560" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D560" s="4" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E560" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F560" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G560" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H560" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I560" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J560" s="4">
+        <v>0</v>
+      </c>
+      <c r="K560" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L560" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="4">
+        <v>544</v>
+      </c>
+      <c r="B561" s="4" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C561" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D561" s="4" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E561" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F561" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G561" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H561" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I561" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J561" s="4">
+        <v>0</v>
+      </c>
+      <c r="K561" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L561" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="4">
+        <v>545</v>
+      </c>
+      <c r="B562" s="4" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C562" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D562" s="4" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E562" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F562" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G562" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H562" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I562" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J562" s="4">
+        <v>0</v>
+      </c>
+      <c r="K562" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L562" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="4">
+        <v>546</v>
+      </c>
+      <c r="B563" s="4" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C563" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D563" s="4" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E563" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F563" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G563" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H563" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I563" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J563" s="4">
+        <v>0</v>
+      </c>
+      <c r="K563" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L563" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="4">
+        <v>547</v>
+      </c>
+      <c r="B564" s="4" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C564" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D564" s="4" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E564" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F564" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G564" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H564" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I564" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J564" s="4">
+        <v>0</v>
+      </c>
+      <c r="K564" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L564" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="4">
+        <v>548</v>
+      </c>
+      <c r="B565" s="4" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C565" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D565" s="4" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E565" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F565" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G565" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H565" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I565" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J565" s="4">
+        <v>0</v>
+      </c>
+      <c r="K565" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L565" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="4">
+        <v>549</v>
+      </c>
+      <c r="B566" s="4" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C566" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D566" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E566" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F566" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G566" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H566" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I566" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J566" s="4">
+        <v>0</v>
+      </c>
+      <c r="K566" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L566" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B568" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D568" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E568">
+        <v>549</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-06.xlsx
+++ b/report-2026-06-06.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="1152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="1156">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-06T02:14:57+05:30</t>
+    <t>Generated 2026-06-06T02:21:01+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-06T02:12:57+05:30 (2m0s ago)</t>
+    <t>2026-06-06T02:19:01+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -3466,10 +3466,22 @@
     <t>02:12:57.441</t>
   </si>
   <si>
+    <t>2026-06-06T02:17:58.646138+05:30</t>
+  </si>
+  <si>
+    <t>02:17:58.646</t>
+  </si>
+  <si>
+    <t>2026-06-06T02:19:01.3448451+05:30</t>
+  </si>
+  <si>
+    <t>02:19:01.344</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-06T02:14:57+05:30</t>
+    <t>2026-06-06T02:21:01+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -4024,7 +4036,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.59</t>
+          <t>10.0.60</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -4064,12 +4076,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 15s</t>
+          <t>0h 2m 14s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-06 02:12:42</t>
+          <t>2026-06-06 02:18:47</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -4079,12 +4091,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-06 02:12:42</t>
+          <t>2026-06-06 02:18:47</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2h 50m 9s</t>
+          <t>2h 54m 14s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -4094,7 +4106,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>02:14:57</t>
+          <t>02:21:01</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4143,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.59</t>
+          <t>10.0.60</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -4151,17 +4163,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>113683.3</t>
+          <t>110214.7</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -4171,7 +4183,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -4186,12 +4198,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-06 02:12:42</t>
+          <t>2026-06-06 02:18:47</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2h 49m 44s</t>
+          <t>2h 52m 59s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -4201,7 +4213,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>02:14:57</t>
+          <t>02:21:01</t>
         </is>
       </c>
     </row>
@@ -4320,7 +4332,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-06T02:12:57.4419603+05:30</t>
+          <t>2026-06-06T02:19:01.3448451+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4330,7 +4342,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>02:12:57.441</t>
+          <t>02:19:01.344</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -14012,6 +14024,216 @@
         </is>
       </c>
       <c r="G274" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275">
+        <v>1780692604499</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>02:20:04</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>72MYabHy</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276">
+        <v>1780692604755</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>02:20:04</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>72MYabHy</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277">
+        <v>1780692606976</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>02:20:06</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>gGIz8GGT</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278">
+        <v>1780692607134</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>02:20:07</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>gGIz8GGT</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279">
+        <v>1780692607886</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>02:20:07</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>prYYq3pj</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280">
+        <v>1780692608129</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>02:20:08</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>prYYq3pj</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -35063,18 +35285,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="567">
+      <c r="A567" s="4">
+        <v>550</v>
+      </c>
+      <c r="B567" s="4" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C567" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D567" s="4" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E567" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F567" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G567" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H567" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I567" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J567" s="4">
+        <v>0</v>
+      </c>
+      <c r="K567" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L567" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="568">
-      <c r="A568" t="s">
-        <v>1149</v>
-      </c>
-      <c r="B568" t="s">
-        <v>1150</v>
-      </c>
-      <c r="D568" t="s">
+      <c r="A568" s="4">
+        <v>551</v>
+      </c>
+      <c r="B568" s="4" t="s">
         <v>1151</v>
       </c>
-      <c r="E568">
-        <v>549</v>
+      <c r="C568" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D568" s="4" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E568" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F568" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G568" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H568" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I568" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J568" s="4">
+        <v>0</v>
+      </c>
+      <c r="K568" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L568" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B570" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D570" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E570">
+        <v>551</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-06.xlsx
+++ b/report-2026-06-06.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="1156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="1196">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-06T02:21:01+05:30</t>
+    <t>Generated 2026-06-06T12:39:31+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-06T02:19:01+05:30 (2m0s ago)</t>
+    <t>2026-06-06T12:37:31+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -3478,10 +3478,130 @@
     <t>02:19:01.344</t>
   </si>
   <si>
+    <t>2026-06-06T02:24:02.6039292+05:30</t>
+  </si>
+  <si>
+    <t>02:24:02.603</t>
+  </si>
+  <si>
+    <t>2026-06-06T02:29:02.5972012+05:30</t>
+  </si>
+  <si>
+    <t>02:29:02.597</t>
+  </si>
+  <si>
+    <t>2026-06-06T02:34:02.754349+05:30</t>
+  </si>
+  <si>
+    <t>02:34:02.754</t>
+  </si>
+  <si>
+    <t>2026-06-06T02:39:02.6088993+05:30</t>
+  </si>
+  <si>
+    <t>02:39:02.608</t>
+  </si>
+  <si>
+    <t>2026-06-06T02:44:02.6738715+05:30</t>
+  </si>
+  <si>
+    <t>02:44:02.673</t>
+  </si>
+  <si>
+    <t>2026-06-06T02:49:02.6003314+05:30</t>
+  </si>
+  <si>
+    <t>02:49:02.600</t>
+  </si>
+  <si>
+    <t>2026-06-06T02:54:02.634182+05:30</t>
+  </si>
+  <si>
+    <t>02:54:02.634</t>
+  </si>
+  <si>
+    <t>2026-06-06T02:59:02.5326307+05:30</t>
+  </si>
+  <si>
+    <t>02:59:02.532</t>
+  </si>
+  <si>
+    <t>2026-06-06T03:04:02.4988555+05:30</t>
+  </si>
+  <si>
+    <t>03:04:02.498</t>
+  </si>
+  <si>
+    <t>2026-06-06T03:09:02.5174213+05:30</t>
+  </si>
+  <si>
+    <t>03:09:02.517</t>
+  </si>
+  <si>
+    <t>2026-06-06T03:14:03.0156796+05:30</t>
+  </si>
+  <si>
+    <t>03:14:03.015</t>
+  </si>
+  <si>
+    <t>2026-06-06T03:19:02.6230539+05:30</t>
+  </si>
+  <si>
+    <t>03:19:02.623</t>
+  </si>
+  <si>
+    <t>2026-06-06T03:24:02.5271236+05:30</t>
+  </si>
+  <si>
+    <t>03:24:02.527</t>
+  </si>
+  <si>
+    <t>2026-06-06T03:29:02.5720525+05:30</t>
+  </si>
+  <si>
+    <t>03:29:02.572</t>
+  </si>
+  <si>
+    <t>2026-06-06T03:34:02.5814869+05:30</t>
+  </si>
+  <si>
+    <t>03:34:02.581</t>
+  </si>
+  <si>
+    <t>2026-06-06T03:39:02.5788422+05:30</t>
+  </si>
+  <si>
+    <t>03:39:02.578</t>
+  </si>
+  <si>
+    <t>2026-06-06T03:44:02.633002+05:30</t>
+  </si>
+  <si>
+    <t>03:44:02.633</t>
+  </si>
+  <si>
+    <t>2026-06-06T03:49:02.566586+05:30</t>
+  </si>
+  <si>
+    <t>03:49:02.566</t>
+  </si>
+  <si>
+    <t>2026-06-06T03:54:02.8834141+05:30</t>
+  </si>
+  <si>
+    <t>03:54:02.883</t>
+  </si>
+  <si>
+    <t>2026-06-06T12:37:31.4976556+05:30</t>
+  </si>
+  <si>
+    <t>12:37:31.497</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-06T02:21:01+05:30</t>
+    <t>2026-06-06T12:39:31+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -4016,12 +4136,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>192.168.0.111</t>
+          <t>192.168.0.164</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>103.117.15.39</t>
+          <t>43.247.40.101</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4036,7 +4156,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.60</t>
+          <t>10.0.37</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -4076,12 +4196,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 14s</t>
+          <t>0h 2m 15s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-06 02:18:47</t>
+          <t>2026-06-06 12:37:16</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -4091,12 +4211,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-06 02:18:47</t>
+          <t>2026-06-06 12:37:16</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2h 54m 14s</t>
+          <t>3h 58m 9s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -4106,7 +4226,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>02:21:01</t>
+          <t>12:39:31</t>
         </is>
       </c>
     </row>
@@ -4123,12 +4243,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>192.168.0.111</t>
+          <t>192.168.0.164</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>103.117.15.39</t>
+          <t>43.247.40.101</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4143,7 +4263,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.60</t>
+          <t>10.0.37</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -4163,17 +4283,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>170.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>110214.7</t>
+          <t>144987.9</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>716</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -4183,7 +4303,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -4198,12 +4318,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-06 02:18:47</t>
+          <t>2026-06-06 12:37:16</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2h 52m 59s</t>
+          <t>3h 56m 44s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -4213,7 +4333,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>02:21:01</t>
+          <t>12:39:31</t>
         </is>
       </c>
     </row>
@@ -4332,7 +4452,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-06T02:19:01.3448451+05:30</t>
+          <t>2026-06-06T12:37:31.4976556+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4342,7 +4462,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>02:19:01.344</t>
+          <t>12:37:31.497</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -35361,18 +35481,778 @@
         <v>43</v>
       </c>
     </row>
+    <row r="569">
+      <c r="A569" s="4">
+        <v>552</v>
+      </c>
+      <c r="B569" s="4" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C569" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D569" s="4" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E569" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F569" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G569" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H569" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I569" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J569" s="4">
+        <v>0</v>
+      </c>
+      <c r="K569" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L569" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="570">
-      <c r="A570" t="s">
-        <v>1153</v>
-      </c>
-      <c r="B570" t="s">
-        <v>1154</v>
-      </c>
-      <c r="D570" t="s">
+      <c r="A570" s="4">
+        <v>553</v>
+      </c>
+      <c r="B570" s="4" t="s">
         <v>1155</v>
       </c>
-      <c r="E570">
-        <v>551</v>
+      <c r="C570" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D570" s="4" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E570" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F570" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G570" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H570" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I570" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J570" s="4">
+        <v>0</v>
+      </c>
+      <c r="K570" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L570" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="4">
+        <v>554</v>
+      </c>
+      <c r="B571" s="4" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C571" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D571" s="4" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E571" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F571" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G571" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H571" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I571" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J571" s="4">
+        <v>0</v>
+      </c>
+      <c r="K571" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L571" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="4">
+        <v>555</v>
+      </c>
+      <c r="B572" s="4" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C572" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D572" s="4" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E572" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F572" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G572" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H572" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I572" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J572" s="4">
+        <v>0</v>
+      </c>
+      <c r="K572" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L572" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="4">
+        <v>556</v>
+      </c>
+      <c r="B573" s="4" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C573" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D573" s="4" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E573" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F573" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G573" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H573" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I573" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J573" s="4">
+        <v>0</v>
+      </c>
+      <c r="K573" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L573" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="4">
+        <v>557</v>
+      </c>
+      <c r="B574" s="4" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C574" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D574" s="4" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E574" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F574" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G574" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H574" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I574" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J574" s="4">
+        <v>0</v>
+      </c>
+      <c r="K574" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L574" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="4">
+        <v>558</v>
+      </c>
+      <c r="B575" s="4" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C575" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D575" s="4" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E575" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F575" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G575" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H575" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I575" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J575" s="4">
+        <v>0</v>
+      </c>
+      <c r="K575" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L575" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="4">
+        <v>559</v>
+      </c>
+      <c r="B576" s="4" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C576" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D576" s="4" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E576" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F576" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G576" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H576" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I576" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J576" s="4">
+        <v>0</v>
+      </c>
+      <c r="K576" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L576" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="4">
+        <v>560</v>
+      </c>
+      <c r="B577" s="4" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C577" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D577" s="4" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E577" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F577" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G577" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H577" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I577" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J577" s="4">
+        <v>0</v>
+      </c>
+      <c r="K577" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L577" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="4">
+        <v>561</v>
+      </c>
+      <c r="B578" s="4" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C578" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D578" s="4" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E578" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F578" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G578" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H578" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I578" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J578" s="4">
+        <v>0</v>
+      </c>
+      <c r="K578" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L578" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="4">
+        <v>562</v>
+      </c>
+      <c r="B579" s="4" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C579" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D579" s="4" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E579" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F579" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G579" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H579" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I579" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J579" s="4">
+        <v>0</v>
+      </c>
+      <c r="K579" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L579" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="4">
+        <v>563</v>
+      </c>
+      <c r="B580" s="4" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C580" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D580" s="4" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E580" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F580" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G580" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H580" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I580" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J580" s="4">
+        <v>0</v>
+      </c>
+      <c r="K580" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L580" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="4">
+        <v>564</v>
+      </c>
+      <c r="B581" s="4" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C581" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D581" s="4" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E581" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F581" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G581" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H581" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I581" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J581" s="4">
+        <v>0</v>
+      </c>
+      <c r="K581" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L581" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="4">
+        <v>565</v>
+      </c>
+      <c r="B582" s="4" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C582" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D582" s="4" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E582" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F582" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G582" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H582" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I582" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J582" s="4">
+        <v>0</v>
+      </c>
+      <c r="K582" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L582" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="4">
+        <v>566</v>
+      </c>
+      <c r="B583" s="4" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C583" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D583" s="4" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E583" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F583" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G583" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H583" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I583" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J583" s="4">
+        <v>0</v>
+      </c>
+      <c r="K583" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L583" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="4">
+        <v>567</v>
+      </c>
+      <c r="B584" s="4" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C584" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D584" s="4" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E584" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F584" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G584" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H584" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I584" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J584" s="4">
+        <v>0</v>
+      </c>
+      <c r="K584" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L584" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="4">
+        <v>568</v>
+      </c>
+      <c r="B585" s="4" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C585" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D585" s="4" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E585" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F585" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G585" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H585" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I585" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J585" s="4">
+        <v>0</v>
+      </c>
+      <c r="K585" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L585" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="4">
+        <v>569</v>
+      </c>
+      <c r="B586" s="4" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C586" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D586" s="4" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E586" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F586" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G586" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H586" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I586" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J586" s="4">
+        <v>0</v>
+      </c>
+      <c r="K586" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L586" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="4">
+        <v>570</v>
+      </c>
+      <c r="B587" s="4" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C587" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D587" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E587" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F587" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G587" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H587" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I587" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J587" s="4">
+        <v>0</v>
+      </c>
+      <c r="K587" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L587" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="4">
+        <v>571</v>
+      </c>
+      <c r="B588" s="4" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C588" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D588" s="4" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E588" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F588" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G588" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H588" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I588" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J588" s="4">
+        <v>0</v>
+      </c>
+      <c r="K588" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L588" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B590" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D590" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E590">
+        <v>571</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-06.xlsx
+++ b/report-2026-06-06.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="1196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="1200">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-06T12:39:31+05:30</t>
+    <t>Generated 2026-06-06T12:43:45+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-06T12:37:31+05:30 (2m0s ago)</t>
+    <t>2026-06-06T12:41:45+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -3598,10 +3598,22 @@
     <t>12:37:31.497</t>
   </si>
   <si>
+    <t>2026-06-06T12:40:03.0204921+05:30</t>
+  </si>
+  <si>
+    <t>12:40:03.020</t>
+  </si>
+  <si>
+    <t>2026-06-06T12:41:45.8254272+05:30</t>
+  </si>
+  <si>
+    <t>12:41:45.825</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-06T12:39:31+05:30</t>
+    <t>2026-06-06T12:43:46+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -4156,7 +4168,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.37</t>
+          <t>10.0.60</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -4196,12 +4208,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 15s</t>
+          <t>0h 2m 14s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-06 12:37:16</t>
+          <t>2026-06-06 12:41:31</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -4211,12 +4223,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-06 12:37:16</t>
+          <t>2026-06-06 12:41:31</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>3h 58m 9s</t>
+          <t>3h 58m 34s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -4226,7 +4238,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>12:39:31</t>
+          <t>12:43:45</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4275,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.37</t>
+          <t>10.0.60</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -4283,17 +4295,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>330.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>144987.9</t>
+          <t>113638.3</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>671</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -4318,12 +4330,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-06 12:37:16</t>
+          <t>2026-06-06 12:41:31</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>3h 56m 44s</t>
+          <t>3h 58m 19s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -4333,217 +4345,324 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>12:39:31</t>
+          <t>12:43:45</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>── LATEST GITHUB ELECTION EVENT ──</t>
+          <t>Dual-89e4fa7c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t/>
+          <t>Dual</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t/>
+          <t>192.168.31.110</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t/>
+          <t>49.36.213.176</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t/>
+          <t>windows</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t/>
+          <t>amd64</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t/>
+          <t>10.0.58</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t/>
+          <t>agent</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t/>
+          <t>websocket</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t/>
+          <t>good</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t/>
+          <t>1060.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t/>
+          <t>239784.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t/>
+          <t>83</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.5</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t/>
+          <t>135</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t/>
+          <t>—</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t/>
+          <t>—</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t/>
+          <t>—</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t/>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t/>
+          <t>12:43:45</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>── LATEST GITHUB ELECTION EVENT ──</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>[renewed]</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-06T12:37:31.4976556+05:30</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-06T12:41:45.8254272+05:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>12:37:31.497</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>12:41:45.825</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>renewed</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>github</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>PuneetU-EB6LMJD-cf4a9ce5</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>PuneetU-EB6LMJD</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>PuneetU-EB6LMJD-cf4a9ce5</t>
         </is>
       </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>renewed</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -36241,18 +36360,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="589">
+      <c r="A589" s="4">
+        <v>572</v>
+      </c>
+      <c r="B589" s="4" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C589" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D589" s="4" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E589" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F589" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G589" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H589" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I589" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J589" s="4">
+        <v>0</v>
+      </c>
+      <c r="K589" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L589" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="590">
-      <c r="A590" t="s">
-        <v>1193</v>
-      </c>
-      <c r="B590" t="s">
-        <v>1194</v>
-      </c>
-      <c r="D590" t="s">
+      <c r="A590" s="4">
+        <v>573</v>
+      </c>
+      <c r="B590" s="4" t="s">
         <v>1195</v>
       </c>
-      <c r="E590">
-        <v>571</v>
+      <c r="C590" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D590" s="4" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E590" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F590" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G590" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H590" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I590" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J590" s="4">
+        <v>0</v>
+      </c>
+      <c r="K590" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L590" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B592" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D592" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E592">
+        <v>573</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-06.xlsx
+++ b/report-2026-06-06.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="1200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="1284">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-06T12:43:45+05:30</t>
+    <t>Generated 2026-06-06T21:33:52+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-06T12:41:45+05:30 (2m0s ago)</t>
+    <t>2026-06-06T21:31:52+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -3610,10 +3610,262 @@
     <t>12:41:45.825</t>
   </si>
   <si>
+    <t>2026-06-06T12:46:47.2560864+05:30</t>
+  </si>
+  <si>
+    <t>12:46:47.256</t>
+  </si>
+  <si>
+    <t>2026-06-06T12:51:47.1244945+05:30</t>
+  </si>
+  <si>
+    <t>12:51:47.124</t>
+  </si>
+  <si>
+    <t>2026-06-06T12:56:47.2292248+05:30</t>
+  </si>
+  <si>
+    <t>12:56:47.229</t>
+  </si>
+  <si>
+    <t>2026-06-06T13:01:47.7179577+05:30</t>
+  </si>
+  <si>
+    <t>13:01:47.717</t>
+  </si>
+  <si>
+    <t>2026-06-06T13:06:47.4441712+05:30</t>
+  </si>
+  <si>
+    <t>13:06:47.444</t>
+  </si>
+  <si>
+    <t>2026-06-06T13:11:47.2557786+05:30</t>
+  </si>
+  <si>
+    <t>13:11:47.255</t>
+  </si>
+  <si>
+    <t>2026-06-06T13:16:48.7631823+05:30</t>
+  </si>
+  <si>
+    <t>13:16:48.763</t>
+  </si>
+  <si>
+    <t>2026-06-06T13:21:49.4635515+05:30</t>
+  </si>
+  <si>
+    <t>13:21:49.463</t>
+  </si>
+  <si>
+    <t>2026-06-06T13:26:46.9172972+05:30</t>
+  </si>
+  <si>
+    <t>13:26:46.917</t>
+  </si>
+  <si>
+    <t>2026-06-06T13:31:47.348369+05:30</t>
+  </si>
+  <si>
+    <t>13:31:47.348</t>
+  </si>
+  <si>
+    <t>2026-06-06T13:36:47.392442+05:30</t>
+  </si>
+  <si>
+    <t>13:36:47.392</t>
+  </si>
+  <si>
+    <t>2026-06-06T13:41:48.3311396+05:30</t>
+  </si>
+  <si>
+    <t>13:41:48.331</t>
+  </si>
+  <si>
+    <t>2026-06-06T13:46:47.2396639+05:30</t>
+  </si>
+  <si>
+    <t>13:46:47.239</t>
+  </si>
+  <si>
+    <t>2026-06-06T13:51:51.0832952+05:30</t>
+  </si>
+  <si>
+    <t>13:51:51.083</t>
+  </si>
+  <si>
+    <t>2026-06-06T13:56:47.101891+05:30</t>
+  </si>
+  <si>
+    <t>13:56:47.101</t>
+  </si>
+  <si>
+    <t>2026-06-06T14:01:47.0489808+05:30</t>
+  </si>
+  <si>
+    <t>14:01:47.048</t>
+  </si>
+  <si>
+    <t>2026-06-06T15:14:14.354455+05:30</t>
+  </si>
+  <si>
+    <t>15:14:14.354</t>
+  </si>
+  <si>
+    <t>2026-06-06T15:14:19.3587347+05:30</t>
+  </si>
+  <si>
+    <t>15:14:19.358</t>
+  </si>
+  <si>
+    <t>2026-06-06T15:14:26.3679956+05:30</t>
+  </si>
+  <si>
+    <t>15:14:26.367</t>
+  </si>
+  <si>
+    <t>2026-06-06T15:20:38.5562603+05:30</t>
+  </si>
+  <si>
+    <t>15:20:38.556</t>
+  </si>
+  <si>
+    <t>2026-06-06T15:25:38.5558976+05:30</t>
+  </si>
+  <si>
+    <t>15:25:38.555</t>
+  </si>
+  <si>
+    <t>2026-06-06T15:30:38.5562188+05:30</t>
+  </si>
+  <si>
+    <t>15:30:38.556</t>
+  </si>
+  <si>
+    <t>2026-06-06T18:32:51.8844302+05:30</t>
+  </si>
+  <si>
+    <t>18:32:51.884</t>
+  </si>
+  <si>
+    <t>2026-06-06T18:35:33.1574356+05:30</t>
+  </si>
+  <si>
+    <t>18:35:33.157</t>
+  </si>
+  <si>
+    <t>2026-06-06T18:40:30.4555118+05:30</t>
+  </si>
+  <si>
+    <t>18:40:30.455</t>
+  </si>
+  <si>
+    <t>2026-06-06T18:45:38.5555278+05:30</t>
+  </si>
+  <si>
+    <t>18:45:38.555</t>
+  </si>
+  <si>
+    <t>2026-06-06T18:45:40.5835175+05:30</t>
+  </si>
+  <si>
+    <t>18:45:40.583</t>
+  </si>
+  <si>
+    <t>2026-06-06T18:50:31.2008843+05:30</t>
+  </si>
+  <si>
+    <t>18:50:31.200</t>
+  </si>
+  <si>
+    <t>2026-06-06T18:55:29.8174079+05:30</t>
+  </si>
+  <si>
+    <t>18:55:29.817</t>
+  </si>
+  <si>
+    <t>2026-06-06T19:00:38.5549153+05:30</t>
+  </si>
+  <si>
+    <t>19:00:38.554</t>
+  </si>
+  <si>
+    <t>2026-06-06T19:05:38.5558702+05:30</t>
+  </si>
+  <si>
+    <t>19:05:38.555</t>
+  </si>
+  <si>
+    <t>2026-06-06T19:10:38.5551272+05:30</t>
+  </si>
+  <si>
+    <t>19:10:38.555</t>
+  </si>
+  <si>
+    <t>2026-06-06T19:47:29.2654343+05:30</t>
+  </si>
+  <si>
+    <t>19:47:29.265</t>
+  </si>
+  <si>
+    <t>2026-06-06T19:50:29.9532522+05:30</t>
+  </si>
+  <si>
+    <t>19:50:29.953</t>
+  </si>
+  <si>
+    <t>2026-06-06T19:55:29.834916+05:30</t>
+  </si>
+  <si>
+    <t>19:55:29.834</t>
+  </si>
+  <si>
+    <t>2026-06-06T20:00:38.5548904+05:30</t>
+  </si>
+  <si>
+    <t>20:00:38.554</t>
+  </si>
+  <si>
+    <t>2026-06-06T20:00:48.5552444+05:30</t>
+  </si>
+  <si>
+    <t>20:00:48.555</t>
+  </si>
+  <si>
+    <t>2026-06-06T20:05:30.0395294+05:30</t>
+  </si>
+  <si>
+    <t>20:05:30.039</t>
+  </si>
+  <si>
+    <t>2026-06-06T20:10:30.0757021+05:30</t>
+  </si>
+  <si>
+    <t>20:10:30.075</t>
+  </si>
+  <si>
+    <t>2026-06-06T20:15:31.1592802+05:30</t>
+  </si>
+  <si>
+    <t>20:15:31.159</t>
+  </si>
+  <si>
+    <t>2026-06-06T21:08:03.4430969+05:30</t>
+  </si>
+  <si>
+    <t>21:08:03.443</t>
+  </si>
+  <si>
+    <t>2026-06-06T21:31:52.053887+05:30</t>
+  </si>
+  <si>
+    <t>21:31:52.053</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-06T12:43:46+05:30</t>
+    <t>2026-06-06T21:33:52+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -4168,7 +4420,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.60</t>
+          <t>10.0.61</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -4208,27 +4460,27 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 14s</t>
+          <t>0h 2m 19s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-06 12:41:31</t>
+          <t>2026-06-06 21:31:33</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Jun 5 07:25 PM</t>
+          <t>Jun 6 03:12 PM</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-06 12:41:31</t>
+          <t>2026-06-06 21:31:33</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>3h 58m 34s</t>
+          <t>1h 25m 36s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -4238,7 +4490,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>12:43:45</t>
+          <t>21:33:52</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4527,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.60</t>
+          <t>10.0.61</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -4295,17 +4547,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>330.0</t>
+          <t>301.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>113638.3</t>
+          <t>118930.3</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>467</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -4315,7 +4567,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -4325,17 +4577,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Jun 5 07:25 PM</t>
+          <t>Jun 6 03:12 PM</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-06 12:41:31</t>
+          <t>2026-06-06 21:31:33</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>3h 58m 19s</t>
+          <t>1h 23m 36s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -4345,324 +4597,217 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>12:43:45</t>
+          <t>21:33:52</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dual-89e4fa7c</t>
+          <t>── LATEST GITHUB ELECTION EVENT ──</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dual</t>
+          <t/>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>192.168.31.110</t>
+          <t/>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>49.36.213.176</t>
+          <t/>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>windows</t>
+          <t/>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>amd64</t>
+          <t/>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.0.58</t>
+          <t/>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t/>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>websocket</t>
+          <t/>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>good</t>
+          <t/>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1060.0</t>
+          <t/>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>239784.0</t>
+          <t/>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>83</t>
+          <t/>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t/>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>135</t>
+          <t/>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t/>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t/>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t/>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t/>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t/>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>12:43:45</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>── LATEST GITHUB ELECTION EVENT ──</t>
+          <t>[renewed]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>2026-06-06T21:31:52.053887+05:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>21:31:52.053</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>renewed</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>PuneetU-EB6LMJD</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
+        </is>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>renewed</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="U5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>[renewed]</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-06T12:41:45.8254272+05:30</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>12:41:45.825</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>renewed</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>github</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>PuneetU-EB6LMJD</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
-        </is>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>renewed</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -36436,18 +36581,1614 @@
         <v>43</v>
       </c>
     </row>
+    <row r="591">
+      <c r="A591" s="4">
+        <v>574</v>
+      </c>
+      <c r="B591" s="4" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C591" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D591" s="4" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E591" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F591" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G591" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H591" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I591" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J591" s="4">
+        <v>0</v>
+      </c>
+      <c r="K591" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L591" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="592">
-      <c r="A592" t="s">
-        <v>1197</v>
-      </c>
-      <c r="B592" t="s">
-        <v>1198</v>
-      </c>
-      <c r="D592" t="s">
+      <c r="A592" s="4">
+        <v>575</v>
+      </c>
+      <c r="B592" s="4" t="s">
         <v>1199</v>
       </c>
-      <c r="E592">
-        <v>573</v>
+      <c r="C592" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D592" s="4" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E592" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F592" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G592" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H592" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I592" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J592" s="4">
+        <v>0</v>
+      </c>
+      <c r="K592" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L592" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="4">
+        <v>576</v>
+      </c>
+      <c r="B593" s="4" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C593" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D593" s="4" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E593" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F593" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G593" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H593" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I593" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J593" s="4">
+        <v>0</v>
+      </c>
+      <c r="K593" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L593" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="4">
+        <v>577</v>
+      </c>
+      <c r="B594" s="4" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C594" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D594" s="4" t="s">
+        <v>1204</v>
+      </c>
+      <c r="E594" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F594" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G594" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H594" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I594" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J594" s="4">
+        <v>0</v>
+      </c>
+      <c r="K594" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L594" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="4">
+        <v>578</v>
+      </c>
+      <c r="B595" s="4" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C595" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D595" s="4" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E595" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F595" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G595" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H595" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I595" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J595" s="4">
+        <v>0</v>
+      </c>
+      <c r="K595" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L595" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="4">
+        <v>579</v>
+      </c>
+      <c r="B596" s="4" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C596" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D596" s="4" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E596" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F596" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G596" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H596" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I596" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J596" s="4">
+        <v>0</v>
+      </c>
+      <c r="K596" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L596" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="4">
+        <v>580</v>
+      </c>
+      <c r="B597" s="4" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C597" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D597" s="4" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E597" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F597" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G597" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H597" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I597" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J597" s="4">
+        <v>0</v>
+      </c>
+      <c r="K597" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L597" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="4">
+        <v>581</v>
+      </c>
+      <c r="B598" s="4" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C598" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D598" s="4" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E598" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F598" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G598" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H598" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I598" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J598" s="4">
+        <v>0</v>
+      </c>
+      <c r="K598" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L598" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="4">
+        <v>582</v>
+      </c>
+      <c r="B599" s="4" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C599" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D599" s="4" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E599" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F599" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G599" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H599" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I599" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J599" s="4">
+        <v>0</v>
+      </c>
+      <c r="K599" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L599" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="4">
+        <v>583</v>
+      </c>
+      <c r="B600" s="4" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C600" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D600" s="4" t="s">
+        <v>1216</v>
+      </c>
+      <c r="E600" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F600" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G600" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H600" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I600" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J600" s="4">
+        <v>0</v>
+      </c>
+      <c r="K600" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L600" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="4">
+        <v>584</v>
+      </c>
+      <c r="B601" s="4" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C601" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D601" s="4" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E601" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F601" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G601" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H601" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I601" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J601" s="4">
+        <v>0</v>
+      </c>
+      <c r="K601" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L601" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="4">
+        <v>585</v>
+      </c>
+      <c r="B602" s="4" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C602" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D602" s="4" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E602" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F602" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G602" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H602" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I602" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J602" s="4">
+        <v>0</v>
+      </c>
+      <c r="K602" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L602" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="4">
+        <v>586</v>
+      </c>
+      <c r="B603" s="4" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C603" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D603" s="4" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E603" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F603" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G603" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H603" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I603" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J603" s="4">
+        <v>0</v>
+      </c>
+      <c r="K603" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L603" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="4">
+        <v>587</v>
+      </c>
+      <c r="B604" s="4" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C604" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D604" s="4" t="s">
+        <v>1224</v>
+      </c>
+      <c r="E604" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F604" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G604" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H604" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I604" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J604" s="4">
+        <v>0</v>
+      </c>
+      <c r="K604" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L604" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="4">
+        <v>588</v>
+      </c>
+      <c r="B605" s="4" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C605" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D605" s="4" t="s">
+        <v>1226</v>
+      </c>
+      <c r="E605" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F605" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G605" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H605" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I605" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J605" s="4">
+        <v>0</v>
+      </c>
+      <c r="K605" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L605" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="4">
+        <v>589</v>
+      </c>
+      <c r="B606" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C606" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D606" s="4" t="s">
+        <v>1228</v>
+      </c>
+      <c r="E606" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F606" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G606" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H606" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I606" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J606" s="4">
+        <v>0</v>
+      </c>
+      <c r="K606" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L606" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="3">
+        <v>590</v>
+      </c>
+      <c r="B607" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C607" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D607" s="3" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E607" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F607" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G607" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H607" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I607" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J607" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K607" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L607" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="3">
+        <v>591</v>
+      </c>
+      <c r="B608" s="3" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C608" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D608" s="3" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E608" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F608" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G608" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H608" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I608" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J608" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K608" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L608" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="3">
+        <v>592</v>
+      </c>
+      <c r="B609" s="3" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C609" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D609" s="3" t="s">
+        <v>1234</v>
+      </c>
+      <c r="E609" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F609" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G609" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H609" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I609" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J609" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K609" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L609" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="3">
+        <v>593</v>
+      </c>
+      <c r="B610" s="3" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C610" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D610" s="3" t="s">
+        <v>1236</v>
+      </c>
+      <c r="E610" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F610" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G610" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H610" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I610" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J610" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K610" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L610" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="3">
+        <v>594</v>
+      </c>
+      <c r="B611" s="3" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C611" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D611" s="3" t="s">
+        <v>1238</v>
+      </c>
+      <c r="E611" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F611" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G611" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H611" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I611" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J611" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K611" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L611" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="3">
+        <v>595</v>
+      </c>
+      <c r="B612" s="3" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C612" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D612" s="3" t="s">
+        <v>1240</v>
+      </c>
+      <c r="E612" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F612" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G612" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H612" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I612" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J612" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K612" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L612" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="3">
+        <v>596</v>
+      </c>
+      <c r="B613" s="3" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C613" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D613" s="3" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E613" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F613" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G613" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H613" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I613" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J613" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K613" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L613" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="4">
+        <v>597</v>
+      </c>
+      <c r="B614" s="4" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C614" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D614" s="4" t="s">
+        <v>1244</v>
+      </c>
+      <c r="E614" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F614" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G614" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H614" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I614" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J614" s="4">
+        <v>0</v>
+      </c>
+      <c r="K614" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L614" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="4">
+        <v>598</v>
+      </c>
+      <c r="B615" s="4" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C615" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D615" s="4" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E615" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F615" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G615" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H615" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I615" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J615" s="4">
+        <v>0</v>
+      </c>
+      <c r="K615" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L615" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="3">
+        <v>599</v>
+      </c>
+      <c r="B616" s="3" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C616" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D616" s="3" t="s">
+        <v>1248</v>
+      </c>
+      <c r="E616" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F616" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G616" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H616" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I616" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J616" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K616" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L616" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="3">
+        <v>600</v>
+      </c>
+      <c r="B617" s="3" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C617" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D617" s="3" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E617" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F617" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G617" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H617" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I617" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J617" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K617" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L617" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="4">
+        <v>601</v>
+      </c>
+      <c r="B618" s="4" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C618" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D618" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="E618" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F618" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G618" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H618" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I618" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J618" s="4">
+        <v>0</v>
+      </c>
+      <c r="K618" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L618" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="4">
+        <v>602</v>
+      </c>
+      <c r="B619" s="4" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C619" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D619" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="E619" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F619" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G619" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H619" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I619" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J619" s="4">
+        <v>0</v>
+      </c>
+      <c r="K619" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L619" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="3">
+        <v>603</v>
+      </c>
+      <c r="B620" s="3" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C620" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D620" s="3" t="s">
+        <v>1256</v>
+      </c>
+      <c r="E620" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F620" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G620" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H620" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I620" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J620" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K620" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L620" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="3">
+        <v>604</v>
+      </c>
+      <c r="B621" s="3" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C621" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D621" s="3" t="s">
+        <v>1258</v>
+      </c>
+      <c r="E621" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F621" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G621" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H621" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I621" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J621" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K621" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L621" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="3">
+        <v>605</v>
+      </c>
+      <c r="B622" s="3" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C622" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D622" s="3" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E622" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F622" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G622" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H622" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I622" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J622" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K622" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L622" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="3">
+        <v>606</v>
+      </c>
+      <c r="B623" s="3" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C623" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D623" s="3" t="s">
+        <v>1262</v>
+      </c>
+      <c r="E623" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F623" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G623" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H623" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I623" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J623" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K623" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L623" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="4">
+        <v>607</v>
+      </c>
+      <c r="B624" s="4" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C624" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D624" s="4" t="s">
+        <v>1264</v>
+      </c>
+      <c r="E624" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F624" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G624" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H624" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I624" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J624" s="4">
+        <v>0</v>
+      </c>
+      <c r="K624" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L624" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="4">
+        <v>608</v>
+      </c>
+      <c r="B625" s="4" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C625" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D625" s="4" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E625" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F625" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G625" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H625" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I625" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J625" s="4">
+        <v>0</v>
+      </c>
+      <c r="K625" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L625" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="3">
+        <v>609</v>
+      </c>
+      <c r="B626" s="3" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C626" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D626" s="3" t="s">
+        <v>1268</v>
+      </c>
+      <c r="E626" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F626" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G626" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H626" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I626" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J626" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K626" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L626" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="3">
+        <v>610</v>
+      </c>
+      <c r="B627" s="3" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C627" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D627" s="3" t="s">
+        <v>1270</v>
+      </c>
+      <c r="E627" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F627" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G627" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H627" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I627" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J627" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K627" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L627" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="4">
+        <v>611</v>
+      </c>
+      <c r="B628" s="4" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C628" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D628" s="4" t="s">
+        <v>1272</v>
+      </c>
+      <c r="E628" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F628" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G628" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H628" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I628" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J628" s="4">
+        <v>0</v>
+      </c>
+      <c r="K628" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L628" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="4">
+        <v>612</v>
+      </c>
+      <c r="B629" s="4" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C629" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D629" s="4" t="s">
+        <v>1274</v>
+      </c>
+      <c r="E629" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F629" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G629" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H629" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I629" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J629" s="4">
+        <v>0</v>
+      </c>
+      <c r="K629" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L629" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="4">
+        <v>613</v>
+      </c>
+      <c r="B630" s="4" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C630" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D630" s="4" t="s">
+        <v>1276</v>
+      </c>
+      <c r="E630" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F630" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G630" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H630" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I630" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J630" s="4">
+        <v>0</v>
+      </c>
+      <c r="K630" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L630" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="4">
+        <v>614</v>
+      </c>
+      <c r="B631" s="4" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C631" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D631" s="4" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E631" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F631" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G631" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H631" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I631" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J631" s="4">
+        <v>0</v>
+      </c>
+      <c r="K631" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L631" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="4">
+        <v>615</v>
+      </c>
+      <c r="B632" s="4" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C632" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D632" s="4" t="s">
+        <v>1280</v>
+      </c>
+      <c r="E632" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F632" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G632" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H632" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I632" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J632" s="4">
+        <v>0</v>
+      </c>
+      <c r="K632" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L632" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B634" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D634" t="s">
+        <v>1283</v>
+      </c>
+      <c r="E634">
+        <v>615</v>
       </c>
     </row>
   </sheetData>
